--- a/results/final_20260514_v2_summary/GpositivePseAAC_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/GpositivePseAAC_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.5086±0.0381</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.4127±0.1099</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2936±0.1226</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.3221±0.1396</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.8685±0.0123</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.8998±0.0150</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.9363±0.0194</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.9487±0.0198</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.7273±0.0232</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.7453±0.0316</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.7743±0.0535</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.7303±0.0720</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7253±0.0246</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.7501±0.0308</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.7851±0.0514</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.7571±0.0676</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.7257±0.0240</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.7462±0.0313</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.7773±0.0527</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.7390±0.0702</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.8487±0.0168</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8630±0.0198</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8795±0.0311</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.8383±0.0484</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.7243±0.0244</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.7432±0.0324</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.7725±0.0536</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7296±0.0725</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5359±0.0205</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5690±0.0279</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6090±0.0644</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5834±0.0586</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5659±0.0170</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5731±0.0333</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5896±0.0707</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5455±0.0728</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5398±0.0241</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5901±0.0333</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6542±0.0624</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6585±0.0644</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.8740±0.2536</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.7126±0.3096</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7099±0.2830</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.7305±0.0250</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.7709±0.0313</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.8179±0.0474</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.7942±0.0618</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.7198±0.0232</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.7394±0.0335</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.7647±0.0537</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.7129±0.0746</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7416±0.0277</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.8054±0.0318</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.8800±0.0451</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.8998±0.0546</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.7264±0.0247</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.7618±0.0351</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.8242±0.0511</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.8444±0.0556</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.7204±0.0259</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.7342±0.0363</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.7582±0.0574</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.7019±0.0815</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.5017±0.0389</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.4112±0.1094</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2935±0.1223</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.3263±0.1364</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.8675±0.0112</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.8991±0.0149</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.9356±0.0195</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.9482±0.0196</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.7283±0.0213</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.7444±0.0313</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.7725±0.0532</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7282±0.0709</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7312±0.0226</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7536±0.0297</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7851±0.0514</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7568±0.0678</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.7283±0.0217</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.7468±0.0307</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.7761±0.0524</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.7375±0.0695</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.8476±0.0159</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8621±0.0198</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.8783±0.0308</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.8363±0.0477</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7253±0.0216</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7423±0.0322</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7707±0.0533</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7276±0.0715</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.5360±0.0179</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.5697±0.0264</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6076±0.0645</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.5814±0.0572</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5600±0.0148</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.5711±0.0331</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.5871±0.0715</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.5426±0.0702</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.5438±0.0225</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.5939±0.0326</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6542±0.0624</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6575±0.0637</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8740±0.2535</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7135±0.3088</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7082±0.2819</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.7306±0.0229</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.7705±0.0306</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.8164±0.0469</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7920±0.0609</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.7158±0.0201</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.7361±0.0341</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.7621±0.0535</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7096±0.0729</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7461±0.0265</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.8087±0.0305</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.8800±0.0451</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.8994±0.0539</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.7226±0.0213</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.7572±0.0367</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.8215±0.0519</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.8428±0.0556</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.7165±0.0225</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.7290±0.0380</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.7546±0.0577</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6981±0.0798</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.5062±0.0391</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.4129±0.1102</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2936±0.1226</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.3220±0.1397</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.8695±0.0117</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.8999±0.0149</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.9363±0.0194</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.9487±0.0198</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.7293±0.0238</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.7455±0.0312</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.7743±0.0535</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.7303±0.0720</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7273±0.0249</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.7501±0.0308</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7851±0.0514</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.7571±0.0676</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.7277±0.0244</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.7463±0.0311</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.7773±0.0527</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.7390±0.0702</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.8497±0.0161</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8631±0.0196</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8795±0.0311</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.8383±0.0484</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.7263±0.0248</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.7434±0.0320</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.7725±0.0536</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.7296±0.0725</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.5374±0.0194</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5692±0.0276</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.6090±0.0644</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.5835±0.0587</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5669±0.0155</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5737±0.0331</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5896±0.0707</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5457±0.0728</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5412±0.0232</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5901±0.0333</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.6542±0.0624</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.6585±0.0644</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.8740±0.2536</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.7126±0.3096</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7132±0.2810</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.7324±0.0242</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.7710±0.0310</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.8179±0.0474</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.7942±0.0618</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.7217±0.0226</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.7397±0.0331</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.7647±0.0537</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.7129±0.0746</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7435±0.0266</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.8054±0.0318</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.8800±0.0451</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.8998±0.0546</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.7283±0.0252</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.7622±0.0347</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.8242±0.0511</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.8444±0.0556</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.7224±0.0262</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.7346±0.0356</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.7582±0.0574</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.7019±0.0815</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.4985±0.0393</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.4110±0.1094</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2941±0.1220</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.3261±0.1365</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.8680±0.0109</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.8990±0.0150</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.9356±0.0196</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.9482±0.0196</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.7293±0.0226</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.7444±0.0314</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.7728±0.0535</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.7282±0.0709</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.7332±0.0233</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.7540±0.0296</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.7856±0.0521</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.7568±0.0678</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.7296±0.0228</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.7469±0.0307</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.7765±0.0528</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.7375±0.0695</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.8480±0.0153</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8620±0.0199</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.8783±0.0310</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.8363±0.0477</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.7264±0.0230</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.7423±0.0323</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.7710±0.0536</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.7276±0.0715</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.5369±0.0173</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.5695±0.0265</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.6075±0.0646</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.5815±0.0572</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5590±0.0104</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.5708±0.0333</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.5868±0.0718</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.5427±0.0702</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.5451±0.0219</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.5939±0.0326</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.6544±0.0624</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.6575±0.0637</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8740±0.2535</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.7135±0.3088</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.7115±0.2799</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.7318±0.0226</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.7705±0.0307</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.8164±0.0472</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.7920±0.0609</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.7164±0.0200</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.7359±0.0342</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.7619±0.0539</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.7096±0.0729</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7481±0.0258</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.8088±0.0305</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.8806±0.0455</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.8994±0.0539</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.7226±0.0243</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.7568±0.0369</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.8215±0.0519</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.8428±0.0556</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.7165±0.0253</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.7286±0.0382</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.7546±0.0577</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.6981±0.0798</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.5018±0.0416</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.4773±0.0624</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.4560±0.0793</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.3954±0.1231</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.8675±0.0119</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.8737±0.0131</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8731±0.0218</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.8408±0.0302</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.7255±0.0191</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.7240±0.0280</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.7141±0.0374</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.6528±0.0405</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.7236±0.0233</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.7298±0.0307</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.7387±0.0368</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.7221±0.0385</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.7239±0.0212</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.7250±0.0289</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.7216±0.0366</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.6750±0.0380</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.8494±0.0147</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8511±0.0163</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8448±0.0217</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.8057±0.0253</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.7226±0.0215</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.7214±0.0286</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.7121±0.0371</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.6506±0.0410</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.5349±0.0197</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.5401±0.0276</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.5388±0.0316</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.5232±0.0510</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.5609±0.0220</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.5527±0.0342</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.5350±0.0396</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.4901±0.0537</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.5410±0.0223</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.5548±0.0295</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.5704±0.0346</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.5869±0.0518</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9757±0.1191</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9720±0.1191</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8385±0.2408</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.7302±0.0233</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.7374±0.0271</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.7345±0.0372</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.6876±0.0439</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.7182±0.0217</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.7152±0.0270</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.6945±0.0394</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.6150±0.0437</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.7426±0.0258</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.7612±0.0301</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.7800±0.0386</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.7806±0.0485</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.7225±0.0226</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.7194±0.0278</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.7009±0.0468</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.5939±0.0646</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.7187±0.0225</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.7104±0.0286</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.6835±0.0421</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.5775±0.0575</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.4954±0.0414</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.4762±0.0371</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.4300±0.0773</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.3946±0.1181</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.8675±0.0104</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.8699±0.0113</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8648±0.0203</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.8135±0.0363</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.7279±0.0162</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.7192±0.0250</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.7009±0.0343</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.6135±0.0466</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7328±0.0207</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.7388±0.0256</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7573±0.0349</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7512±0.0360</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.7286±0.0180</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.7249±0.0247</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.7190±0.0328</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.6580±0.0377</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.8501±0.0138</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.8477±0.0147</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.8359±0.0192</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.7750±0.0302</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.7250±0.0177</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.7167±0.0251</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.6991±0.0345</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.6115±0.0469</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.5377±0.0170</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.5406±0.0243</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.5348±0.0270</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.5002±0.0401</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5590±0.0219</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.5425±0.0359</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.5085±0.0372</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.4363±0.0413</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.5475±0.0201</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.5645±0.0251</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5885±0.0330</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.6143±0.0644</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9714±0.1143</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8544±0.2355</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.7322±0.0206</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.7350±0.0227</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.7276±0.0313</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.6631±0.0419</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.7162±0.0211</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.7027±0.0259</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.6673±0.0369</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.5628±0.0462</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.7490±0.0218</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7707±0.0230</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.8009±0.0327</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.8090±0.0400</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.7187±0.0182</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.7005±0.0278</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.6581±0.0527</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.4925±0.0925</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.7142±0.0183</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.6923±0.0287</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.6394±0.0478</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.4746±0.0836</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.5046±0.0380</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.4775±0.0621</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.4548±0.0798</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.3981±0.1252</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.8666±0.0102</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.8740±0.0127</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8733±0.0214</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.8419±0.0300</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.7236±0.0155</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.7246±0.0270</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.7126±0.0371</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.6543±0.0402</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.7217±0.0197</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.7298±0.0301</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.7356±0.0362</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.7200±0.0399</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.7220±0.0177</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.7255±0.0281</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.7196±0.0363</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.6754±0.0384</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.8487±0.0127</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8517±0.0156</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8449±0.0216</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.8068±0.0253</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.7207±0.0179</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.7220±0.0277</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.7106±0.0370</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.6521±0.0407</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.5329±0.0158</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.5408±0.0271</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.5376±0.0318</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.5221±0.0519</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.5595±0.0209</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.5537±0.0337</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.5334±0.0392</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.4898±0.0538</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.5387±0.0181</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.5552±0.0292</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.5689±0.0345</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.5846±0.0542</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9757±0.1191</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9720±0.1191</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8360±0.2459</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.7282±0.0196</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.7382±0.0264</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.7341±0.0370</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.6881±0.0445</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.7162±0.0181</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.7158±0.0259</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.6941±0.0390</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.6168±0.0432</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.7406±0.0222</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.7622±0.0297</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.7794±0.0380</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7788±0.0508</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.7206±0.0195</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.7202±0.0268</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.7009±0.0464</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.5996±0.0621</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.7168±0.0193</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.7117±0.0276</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.6837±0.0424</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.5826±0.0550</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.4916±0.0358</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.4781±0.0364</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.4248±0.0837</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.3932±0.1181</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.8666±0.0084</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.8692±0.0114</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8646±0.0213</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.8140±0.0360</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.7265±0.0115</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.7184±0.0256</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.7006±0.0361</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.6129±0.0455</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.7334±0.0151</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.7382±0.0261</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7570±0.0353</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7507±0.0365</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.7278±0.0134</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.7243±0.0252</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.7187±0.0342</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.6573±0.0374</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.8492±0.0117</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.8471±0.0144</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.8358±0.0204</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.7751±0.0302</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.7236±0.0140</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.7160±0.0258</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.6987±0.0362</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.6108±0.0459</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.5366±0.0123</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.5405±0.0241</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.5397±0.0381</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.5000±0.0404</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5532±0.0185</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.5430±0.0365</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.5137±0.0444</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.4345±0.0400</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.5484±0.0141</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.5641±0.0240</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.5941±0.0435</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.6159±0.0664</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9514±0.1488</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8541±0.2404</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.7314±0.0158</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.7343±0.0226</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.7278±0.0331</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.6636±0.0420</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.7128±0.0177</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.7018±0.0265</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.6669±0.0388</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.5623±0.0452</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.7510±0.0157</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7703±0.0227</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.8020±0.0339</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.8112±0.0420</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.7148±0.0173</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.6990±0.0295</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.6570±0.0550</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.4921±0.0896</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.7110±0.0165</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.6914±0.0305</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.6390±0.0497</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.4739±0.0807</t>
         </is>
